--- a/downloads/inventory/dixani-reorder-level-tracker.xlsx
+++ b/downloads/inventory/dixani-reorder-level-tracker.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reorder Level Tracker" sheetId="1" r:id="R0a7bea6e25f54e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Rad7e4aa1867543f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" r:id="R4225fca7bdd940d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reorder Level Tracker" sheetId="1" r:id="R977dd4c24db24ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R1f034339556a4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" r:id="R2ce7d1d1738841fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -232,7 +232,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -243,7 +243,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -254,7 +254,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +264,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -275,7 +275,7 @@
         <x:color rgb="FF2563EB"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEFF6FF"/>
         </x:patternFill>
       </x:fill>
@@ -479,7 +479,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
@@ -580,7 +580,7 @@
         <x:v>Currency</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="C5"/>
       <x:c r="D5" s="16" t="str">
@@ -4202,7 +4202,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B5">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E13:E112">
       <x:formula1>"PCS,EA,BOX,CTN,KG,G,L,ML,M,SET,PACK"</x:formula1>
